--- a/backend/local_storage/default/users.xlsx
+++ b/backend/local_storage/default/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>emergency_number</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>employee_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -503,6 +508,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -544,6 +550,7 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -573,6 +580,107 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RV003</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RV@003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mahesh</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hr_test</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>password123</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Test HR User</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hr@example.com</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1234567890</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RV004</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RV@004</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>RV004</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
